--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:55</t>
+    <t xml:space="preserve">2026-08-17 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 14:06</t>
+    <t xml:space="preserve">2026-08-17 22:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 22:18</t>
+    <t xml:space="preserve">2026-09-06 20:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
